--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N114_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N114_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.59192085281862</v>
+        <v>6.271187138583025</v>
       </c>
       <c r="D2" t="n">
-        <v>38.38004099338004</v>
+        <v>6.236756661424256</v>
       </c>
       <c r="E2" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F2" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.10263137648707</v>
+        <v>2.779177598679149</v>
       </c>
       <c r="D3" t="n">
-        <v>28.02718408443014</v>
+        <v>4.554417413719898</v>
       </c>
       <c r="E3" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F3" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.1807193595105</v>
+        <v>3.116866895920456</v>
       </c>
       <c r="D4" t="n">
-        <v>19.18621256868466</v>
+        <v>3.117759542411257</v>
       </c>
       <c r="E4" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F4" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.81845012620441</v>
+        <v>5.170498145508216</v>
       </c>
       <c r="D5" t="n">
-        <v>36.19561749744108</v>
+        <v>5.881787843334175</v>
       </c>
       <c r="E5" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F5" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.36296968015042</v>
+        <v>1.846482573024443</v>
       </c>
       <c r="D6" t="n">
-        <v>23.17784304400724</v>
+        <v>3.766399494651177</v>
       </c>
       <c r="E6" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F6" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.419694320540679</v>
+        <v>0.7182003270878604</v>
       </c>
       <c r="D7" t="n">
-        <v>15.78301654029138</v>
+        <v>2.564740187797349</v>
       </c>
       <c r="E7" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F7" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.68971675780971</v>
+        <v>2.874578973144077</v>
       </c>
       <c r="D8" t="n">
-        <v>19.55354875676237</v>
+        <v>3.177451672973886</v>
       </c>
       <c r="E8" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F8" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.44307134577398</v>
+        <v>3.809499093688272</v>
       </c>
       <c r="D9" t="n">
-        <v>23.81794912152666</v>
+        <v>3.870416732248082</v>
       </c>
       <c r="E9" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F9" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.02609518599329</v>
+        <v>2.60424046772391</v>
       </c>
       <c r="D10" t="n">
-        <v>10.27516841208527</v>
+        <v>1.669714866963856</v>
       </c>
       <c r="E10" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F10" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.80274976142109</v>
+        <v>3.705446836230927</v>
       </c>
       <c r="D11" t="n">
-        <v>26.36194763910147</v>
+        <v>4.283816491353988</v>
       </c>
       <c r="E11" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F11" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>3.485901665051614</v>
+        <v>0.5664590205708874</v>
       </c>
       <c r="D12" t="n">
-        <v>18.80949073001154</v>
+        <v>3.056542243626875</v>
       </c>
       <c r="E12" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F12" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.50567298481561</v>
+        <v>3.982171860032537</v>
       </c>
       <c r="D13" t="n">
-        <v>23.77891819518949</v>
+        <v>3.864074206718293</v>
       </c>
       <c r="E13" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F13" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.18420657455215</v>
+        <v>4.092433568364725</v>
       </c>
       <c r="D14" t="n">
-        <v>24.11706731030434</v>
+        <v>3.919023437924455</v>
       </c>
       <c r="E14" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F14" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>9.290351020173794</v>
+        <v>1.509682040778242</v>
       </c>
       <c r="D15" t="n">
-        <v>9.056781387621609</v>
+        <v>1.471726975488511</v>
       </c>
       <c r="E15" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F15" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>13.60674463148864</v>
+        <v>2.211096002616904</v>
       </c>
       <c r="D16" t="n">
-        <v>16.51137737163601</v>
+        <v>2.683098822890852</v>
       </c>
       <c r="E16" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F16" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>17.97311303171135</v>
+        <v>2.920630867653094</v>
       </c>
       <c r="D17" t="n">
-        <v>21.53142246067188</v>
+        <v>3.49885614985918</v>
       </c>
       <c r="E17" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F17" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>21.42525723567148</v>
+        <v>3.481604300796616</v>
       </c>
       <c r="D18" t="n">
-        <v>21.97074914523151</v>
+        <v>3.570246736100121</v>
       </c>
       <c r="E18" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F18" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>44.75396426112548</v>
+        <v>7.272519192432891</v>
       </c>
       <c r="D19" t="n">
-        <v>43.50512360697698</v>
+        <v>7.06958258613376</v>
       </c>
       <c r="E19" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F19" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>14.27340378662396</v>
+        <v>2.319428115326394</v>
       </c>
       <c r="D20" t="n">
-        <v>34.64475758872933</v>
+        <v>5.629773108168516</v>
       </c>
       <c r="E20" t="n">
-        <v>10.20641218118226</v>
+        <v>1.658541979442118</v>
       </c>
       <c r="F20" t="n">
-        <v>8.847011389414929</v>
+        <v>1.437639350779926</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
